--- a/premise/data/additional_inventories/lci-wave_energy.xlsx
+++ b/premise/data/additional_inventories/lci-wave_energy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40BA64D5-5CF1-0146-A5E0-7E66D83DD6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB7535-F8D6-1649-B31D-A4E1C2DB8F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="600" windowWidth="30240" windowHeight="19640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31660" yWindow="1320" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -933,7 +933,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -941,6 +941,12 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -969,11 +975,11 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1143,4281 +1149,4280 @@
   <dimension ref="A1:Z299"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="48" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48" style="1" customWidth="1"/>
-    <col min="8" max="8" width="72" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="48" customWidth="1"/>
+    <col min="8" max="8" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>152</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>156</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14">
         <v>18</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>151</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="F14" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" t="s">
         <v>157</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>19</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28">
         <f>2.55*43</f>
         <v>109.64999999999999</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="F28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>13</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40">
         <v>1</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="C40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>27</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41">
         <v>533</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" t="s">
         <v>30</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42">
         <v>340</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="D42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>34</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43">
         <v>324</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="1" t="s">
+      <c r="D43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44">
         <v>113.51</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="D44" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" t="s">
         <v>38</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45">
         <v>86.3</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G45" s="1" t="s">
+      <c r="D45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" t="s">
         <v>40</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46">
         <v>59.9</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G46" s="1" t="s">
+      <c r="C46" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" t="s">
         <v>42</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47">
         <v>11</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="D47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" t="s">
         <v>44</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>5</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>12</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="H58" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>45</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59">
         <v>1</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D59" s="1" t="s">
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" t="s">
         <v>18</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" t="s">
         <v>46</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>28</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60">
         <v>5.5043000000000002E-2</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G60" s="1" t="s">
+      <c r="D60" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" t="s">
         <v>30</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>47</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61">
         <v>1.3320000000000001E-3</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G61" s="1" t="s">
+      <c r="D61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" t="s">
         <v>48</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>39</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62">
         <v>0.89900000000000002</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G62" s="1" t="s">
+      <c r="D62" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" t="s">
         <v>40</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>49</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63">
         <v>0.378</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G63" s="1" t="s">
+      <c r="D63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" t="s">
         <v>50</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>51</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64">
         <v>1.6736000000000001E-2</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G64" s="1" t="s">
+      <c r="D64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" t="s">
         <v>52</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>51</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65">
         <v>0.315</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G65" s="1" t="s">
+      <c r="D65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" t="s">
         <v>52</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>53</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="C66" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" t="s">
         <v>54</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>55</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67">
         <v>0.183</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G67" s="1" t="s">
+      <c r="C67" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" t="s">
         <v>56</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" t="s">
         <v>177</v>
       </c>
-      <c r="V67" s="2"/>
+      <c r="V67" s="1"/>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>57</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" t="s">
         <v>21</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G68" s="1" t="s">
+      <c r="D68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" t="s">
         <v>58</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>57</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>21</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G69" s="1" t="s">
+      <c r="D69" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" t="s">
         <v>58</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>59</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G70" s="1" t="s">
+      <c r="D70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" t="s">
         <v>60</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G71" s="1" t="s">
+      <c r="D71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" t="s">
         <v>62</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>63</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72">
         <v>0.22700000000000001</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G72" s="1" t="s">
+      <c r="D72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" t="s">
         <v>64</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73">
         <v>2.3751000000000001E-2</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G73" s="1" t="s">
+      <c r="C73" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" t="s">
         <v>66</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>65</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74">
         <v>0.84399999999999997</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G74" s="1" t="s">
+      <c r="C74" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" t="s">
         <v>66</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>67</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75">
         <v>0.28199999999999997</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G75" s="1" t="s">
+      <c r="C75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D75" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" t="s">
         <v>68</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>69</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76">
         <v>0.19800000000000001</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" t="s">
         <v>32</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G76" s="1" t="s">
+      <c r="D76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" t="s">
         <v>70</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>4</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>5</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>6</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>8</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>10</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>12</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>13</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="D87" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="F87" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G87" s="5" t="s">
+      <c r="G87" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H87" s="5" t="s">
+      <c r="H87" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>71</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88">
         <v>1</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D88" s="1" t="s">
+      <c r="C88" t="s">
+        <v>26</v>
+      </c>
+      <c r="D88" t="s">
         <v>10</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" t="s">
         <v>18</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="G88" t="s">
         <v>72</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H88" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>34</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89">
         <v>89.7</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G89" s="1" t="s">
+      <c r="D89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89" t="s">
+        <v>23</v>
+      </c>
+      <c r="G89" t="s">
         <v>35</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>47</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90">
         <v>6</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" t="s">
         <v>21</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G90" s="1" t="s">
+      <c r="D90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" t="s">
         <v>48</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>51</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91">
         <v>7.6</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" t="s">
         <v>21</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G91" s="1" t="s">
+      <c r="D91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" t="s">
         <v>52</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>69</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92">
         <v>0.4</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" t="s">
         <v>32</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G92" s="1" t="s">
+      <c r="D92" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" t="s">
         <v>70</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="H92" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>57</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93">
         <v>0.9</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" t="s">
         <v>21</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G93" s="1" t="s">
+      <c r="D93" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" t="s">
         <v>58</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H93" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>73</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94">
         <v>0.7</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" t="s">
         <v>21</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G94" s="1" t="s">
+      <c r="D94" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" t="s">
         <v>74</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H94" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>75</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95">
         <v>0.1</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" t="s">
         <v>21</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G95" s="1" t="s">
+      <c r="D95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" t="s">
         <v>76</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H95" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>77</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96">
         <v>0.1</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G96" s="1" t="s">
+      <c r="C96" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" t="s">
+        <v>29</v>
+      </c>
+      <c r="F96" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" t="s">
         <v>78</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="H96" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="97" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>79</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97">
         <v>0.1</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G97" s="1" t="s">
+      <c r="C97" t="s">
+        <v>26</v>
+      </c>
+      <c r="D97" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" t="s">
         <v>80</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H97" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>65</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98">
         <v>22.6</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G98" s="1" t="s">
+      <c r="C98" t="s">
+        <v>26</v>
+      </c>
+      <c r="D98" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" t="s">
         <v>66</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>67</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99">
         <v>0.2</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G99" s="1" t="s">
+      <c r="C99" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" t="s">
         <v>68</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H99" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>81</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100">
         <v>0.5</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" t="s">
         <v>21</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G100" s="1" t="s">
+      <c r="D100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" t="s">
         <v>82</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H100" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="101" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>39</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" t="s">
         <v>21</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G101" s="1" t="s">
+      <c r="D101" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" t="s">
         <v>40</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H101" t="s">
         <v>200</v>
       </c>
-      <c r="Z101" s="3"/>
+      <c r="Z101" s="2"/>
     </row>
     <row r="102" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>83</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102">
         <v>0.8</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G102" s="1" t="s">
+      <c r="C102" t="s">
+        <v>26</v>
+      </c>
+      <c r="D102" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" t="s">
         <v>84</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="H102" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A104" s="5" t="s">
+      <c r="A104" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="105" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>4</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>5</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106">
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>6</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="108" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>8</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>10</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>12</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>13</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="112" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
+      <c r="A113" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B113" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C113" s="5" t="s">
+      <c r="C113" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="5" t="s">
+      <c r="D113" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F113" s="5" t="s">
+      <c r="F113" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="G113" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H113" s="5" t="s">
+      <c r="H113" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>85</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114">
         <v>1</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D114" s="1" t="s">
+      <c r="C114" t="s">
+        <v>26</v>
+      </c>
+      <c r="D114" t="s">
         <v>10</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F114" t="s">
         <v>18</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="G114" t="s">
         <v>86</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="H114" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>71</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115">
         <v>2</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D115" s="1" t="s">
+      <c r="C115" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115" t="s">
         <v>10</v>
       </c>
-      <c r="F115" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G115" s="1" t="s">
+      <c r="F115" t="s">
+        <v>23</v>
+      </c>
+      <c r="G115" t="s">
         <v>72</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="H115" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>45</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116">
         <v>1</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D116" s="1" t="s">
+      <c r="C116" t="s">
+        <v>26</v>
+      </c>
+      <c r="D116" t="s">
         <v>10</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G116" s="1" t="s">
+      <c r="F116" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" t="s">
         <v>46</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="H116" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
+      <c r="A119" t="s">
         <v>4</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
+      <c r="A120" t="s">
         <v>5</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
+      <c r="A121" t="s">
         <v>6</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
+      <c r="A122" t="s">
         <v>8</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
+      <c r="A123" t="s">
         <v>10</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
+      <c r="A124" t="s">
         <v>12</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
+      <c r="A125" t="s">
         <v>13</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="1" t="s">
+      <c r="A126" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="5" t="s">
+      <c r="A127" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="C127" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="5" t="s">
+      <c r="D127" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="E127" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G127" s="5" t="s">
+      <c r="G127" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H127" s="5" t="s">
+      <c r="H127" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
         <v>87</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128">
         <v>1</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F128" s="1" t="s">
+      <c r="C128" t="s">
+        <v>26</v>
+      </c>
+      <c r="D128" t="s">
+        <v>29</v>
+      </c>
+      <c r="F128" t="s">
         <v>18</v>
       </c>
-      <c r="G128" s="1" t="s">
+      <c r="G128" t="s">
         <v>88</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="H128" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="1" t="s">
+      <c r="A129" t="s">
         <v>65</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B129">
         <v>0.15</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G129" s="1" t="s">
+      <c r="C129" t="s">
+        <v>26</v>
+      </c>
+      <c r="D129" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" t="s">
         <v>66</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H129" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="1" t="s">
+      <c r="A130" t="s">
         <v>65</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G130" s="1" t="s">
+      <c r="C130" t="s">
+        <v>26</v>
+      </c>
+      <c r="D130" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130" t="s">
+        <v>23</v>
+      </c>
+      <c r="G130" t="s">
         <v>66</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="H130" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="1" t="s">
+      <c r="A131" t="s">
         <v>89</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G131" s="1" t="s">
+      <c r="C131" t="s">
+        <v>26</v>
+      </c>
+      <c r="D131" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131" t="s">
+        <v>23</v>
+      </c>
+      <c r="G131" t="s">
         <v>90</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="H131" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" s="1" t="s">
+      <c r="A132" t="s">
         <v>91</v>
       </c>
-      <c r="B132" s="1">
+      <c r="B132">
         <v>0.04</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" t="s">
         <v>21</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G132" s="1" t="s">
+      <c r="D132" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132" t="s">
+        <v>23</v>
+      </c>
+      <c r="G132" t="s">
         <v>92</v>
       </c>
-      <c r="H132" s="1" t="s">
+      <c r="H132" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133" s="1" t="s">
+      <c r="A133" t="s">
         <v>93</v>
       </c>
-      <c r="B133" s="1">
+      <c r="B133">
         <v>0.02</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G133" s="1" t="s">
+      <c r="C133" t="s">
+        <v>26</v>
+      </c>
+      <c r="D133" t="s">
+        <v>29</v>
+      </c>
+      <c r="F133" t="s">
+        <v>23</v>
+      </c>
+      <c r="G133" t="s">
         <v>94</v>
       </c>
-      <c r="H133" s="1" t="s">
+      <c r="H133" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="1" t="s">
+      <c r="A134" t="s">
         <v>95</v>
       </c>
-      <c r="B134" s="1">
+      <c r="B134">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G134" s="1" t="s">
+      <c r="C134" t="s">
+        <v>26</v>
+      </c>
+      <c r="D134" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134" t="s">
+        <v>23</v>
+      </c>
+      <c r="G134" t="s">
         <v>96</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="H134" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135" s="1" t="s">
+      <c r="A135" t="s">
         <v>97</v>
       </c>
-      <c r="B135" s="1">
+      <c r="B135">
         <v>0.02</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" t="s">
         <v>21</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G135" s="1" t="s">
+      <c r="D135" t="s">
+        <v>29</v>
+      </c>
+      <c r="F135" t="s">
+        <v>23</v>
+      </c>
+      <c r="G135" t="s">
         <v>98</v>
       </c>
-      <c r="H135" s="1" t="s">
+      <c r="H135" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136" s="1" t="s">
+      <c r="A136" t="s">
         <v>65</v>
       </c>
-      <c r="B136" s="1">
+      <c r="B136">
         <v>0.60250000000000004</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G136" s="1" t="s">
+      <c r="C136" t="s">
+        <v>26</v>
+      </c>
+      <c r="D136" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" t="s">
+        <v>23</v>
+      </c>
+      <c r="G136" t="s">
         <v>66</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="H136" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A138" s="5" t="s">
+      <c r="A138" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B138" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A139" s="1" t="s">
+      <c r="A139" t="s">
         <v>4</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A140" s="1" t="s">
+      <c r="A140" t="s">
         <v>5</v>
       </c>
-      <c r="B140" s="1">
+      <c r="B140">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141" s="1" t="s">
+      <c r="A141" t="s">
         <v>6</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>8</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A143" s="1" t="s">
+      <c r="A143" t="s">
         <v>10</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A144" s="1" t="s">
+      <c r="A144" t="s">
         <v>12</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="145" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A145" s="1" t="s">
+      <c r="A145" t="s">
         <v>13</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="146" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A146" s="1" t="s">
+      <c r="A146" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="147" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A147" s="5" t="s">
+      <c r="A147" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B147" s="5" t="s">
+      <c r="B147" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C147" s="5" t="s">
+      <c r="C147" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="5" t="s">
+      <c r="D147" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E147" s="5" t="s">
+      <c r="E147" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F147" s="5" t="s">
+      <c r="F147" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G147" s="5" t="s">
+      <c r="G147" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H147" s="5" t="s">
+      <c r="H147" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A148" s="1" t="s">
+      <c r="A148" t="s">
         <v>99</v>
       </c>
-      <c r="B148" s="1">
+      <c r="B148">
         <v>1</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F148" s="1" t="s">
+      <c r="C148" t="s">
+        <v>26</v>
+      </c>
+      <c r="D148" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148" t="s">
         <v>18</v>
       </c>
-      <c r="G148" s="1" t="s">
+      <c r="G148" t="s">
         <v>100</v>
       </c>
-      <c r="H148" s="1" t="s">
+      <c r="H148" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="149" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A149" s="1" t="s">
+      <c r="A149" t="s">
         <v>89</v>
       </c>
-      <c r="B149" s="1">
+      <c r="B149">
         <v>0.16250000000000001</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G149" s="1" t="s">
+      <c r="C149" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149" t="s">
+        <v>23</v>
+      </c>
+      <c r="G149" t="s">
         <v>90</v>
       </c>
-      <c r="H149" s="1" t="s">
+      <c r="H149" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="150" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A150" s="1" t="s">
+      <c r="A150" t="s">
         <v>91</v>
       </c>
-      <c r="B150" s="1">
+      <c r="B150">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" t="s">
         <v>21</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G150" s="1" t="s">
+      <c r="D150" t="s">
+        <v>29</v>
+      </c>
+      <c r="F150" t="s">
+        <v>23</v>
+      </c>
+      <c r="G150" t="s">
         <v>92</v>
       </c>
-      <c r="H150" s="1" t="s">
+      <c r="H150" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="151" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A151" s="1" t="s">
+      <c r="A151" t="s">
         <v>101</v>
       </c>
-      <c r="B151" s="1">
+      <c r="B151">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G151" s="1" t="s">
+      <c r="C151" t="s">
+        <v>26</v>
+      </c>
+      <c r="D151" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151" t="s">
+        <v>23</v>
+      </c>
+      <c r="G151" t="s">
         <v>102</v>
       </c>
-      <c r="H151" s="1" t="s">
+      <c r="H151" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="152" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A152" s="1" t="s">
+      <c r="A152" t="s">
         <v>103</v>
       </c>
-      <c r="B152" s="1">
+      <c r="B152">
         <v>0.04</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C152" t="s">
         <v>21</v>
       </c>
-      <c r="D152" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G152" s="1" t="s">
+      <c r="D152" t="s">
+        <v>29</v>
+      </c>
+      <c r="F152" t="s">
+        <v>23</v>
+      </c>
+      <c r="G152" t="s">
         <v>104</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="H152" t="s">
         <v>218</v>
       </c>
-      <c r="T152" s="4"/>
+      <c r="T152" s="3"/>
     </row>
     <row r="153" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A153" s="1" t="s">
+      <c r="A153" t="s">
         <v>105</v>
       </c>
-      <c r="B153" s="1">
+      <c r="B153">
         <v>0.03</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G153" s="1" t="s">
+      <c r="C153" t="s">
+        <v>26</v>
+      </c>
+      <c r="D153" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153" t="s">
+        <v>23</v>
+      </c>
+      <c r="G153" t="s">
         <v>106</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="H153" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="154" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A154" s="1" t="s">
+      <c r="A154" t="s">
         <v>93</v>
       </c>
-      <c r="B154" s="1">
+      <c r="B154">
         <v>0.05</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G154" s="1" t="s">
+      <c r="C154" t="s">
+        <v>26</v>
+      </c>
+      <c r="D154" t="s">
+        <v>29</v>
+      </c>
+      <c r="F154" t="s">
+        <v>23</v>
+      </c>
+      <c r="G154" t="s">
         <v>94</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="H154" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="155" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A155" s="1" t="s">
+      <c r="A155" t="s">
         <v>107</v>
       </c>
-      <c r="B155" s="1">
+      <c r="B155">
         <v>1.7500000000000002E-2</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G155" s="1" t="s">
+      <c r="C155" t="s">
+        <v>26</v>
+      </c>
+      <c r="D155" t="s">
+        <v>29</v>
+      </c>
+      <c r="F155" t="s">
+        <v>23</v>
+      </c>
+      <c r="G155" t="s">
         <v>108</v>
       </c>
-      <c r="H155" s="1" t="s">
+      <c r="H155" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="156" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A156" s="1" t="s">
+      <c r="A156" t="s">
         <v>109</v>
       </c>
-      <c r="B156" s="1">
+      <c r="B156">
         <v>0.02</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C156" t="s">
         <v>21</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G156" s="1" t="s">
+      <c r="D156" t="s">
+        <v>29</v>
+      </c>
+      <c r="F156" t="s">
+        <v>23</v>
+      </c>
+      <c r="G156" t="s">
         <v>110</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="H156" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="157" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A157" s="1" t="s">
+      <c r="A157" t="s">
         <v>107</v>
       </c>
-      <c r="B157" s="1">
+      <c r="B157">
         <v>6.2500000000000003E-3</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G157" s="1" t="s">
+      <c r="C157" t="s">
+        <v>26</v>
+      </c>
+      <c r="D157" t="s">
+        <v>29</v>
+      </c>
+      <c r="F157" t="s">
+        <v>23</v>
+      </c>
+      <c r="G157" t="s">
         <v>108</v>
       </c>
-      <c r="H157" s="1" t="s">
+      <c r="H157" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="158" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A158" s="1" t="s">
+      <c r="A158" t="s">
         <v>65</v>
       </c>
-      <c r="B158" s="1">
+      <c r="B158">
         <v>0.51375000000000004</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G158" s="1" t="s">
+      <c r="C158" t="s">
+        <v>26</v>
+      </c>
+      <c r="D158" t="s">
+        <v>29</v>
+      </c>
+      <c r="F158" t="s">
+        <v>23</v>
+      </c>
+      <c r="G158" t="s">
         <v>66</v>
       </c>
-      <c r="H158" s="1" t="s">
+      <c r="H158" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="160" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A160" s="5" t="s">
+      <c r="A160" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B160" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A161" s="1" t="s">
+      <c r="A161" t="s">
         <v>4</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="B161" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A162" s="1" t="s">
+      <c r="A162" t="s">
         <v>5</v>
       </c>
-      <c r="B162" s="1">
+      <c r="B162">
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163" s="1" t="s">
+      <c r="A163" t="s">
         <v>6</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B163" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A164" s="1" t="s">
+      <c r="A164" t="s">
         <v>8</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B164" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A165" s="1" t="s">
+      <c r="A165" t="s">
         <v>10</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B165" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A166" s="1" t="s">
+      <c r="A166" t="s">
         <v>12</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B166" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A167" s="1" t="s">
+      <c r="A167" t="s">
         <v>13</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B167" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A168" s="1" t="s">
+      <c r="A168" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A169" s="5" t="s">
+      <c r="A169" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="B169" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="C169" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="5" t="s">
+      <c r="D169" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E169" s="5" t="s">
+      <c r="E169" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="F169" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G169" s="5" t="s">
+      <c r="G169" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H169" s="5" t="s">
+      <c r="H169" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A170" s="1" t="s">
+      <c r="A170" t="s">
         <v>111</v>
       </c>
-      <c r="B170" s="1">
+      <c r="B170">
         <v>1</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F170" s="1" t="s">
+      <c r="C170" t="s">
+        <v>26</v>
+      </c>
+      <c r="D170" t="s">
+        <v>29</v>
+      </c>
+      <c r="F170" t="s">
         <v>18</v>
       </c>
-      <c r="G170" s="1" t="s">
+      <c r="G170" t="s">
         <v>112</v>
       </c>
-      <c r="H170" s="1" t="s">
+      <c r="H170" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A171" s="1" t="s">
+      <c r="A171" t="s">
         <v>99</v>
       </c>
-      <c r="B171" s="1">
+      <c r="B171">
         <v>0.156</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G171" s="1" t="s">
+      <c r="C171" t="s">
+        <v>26</v>
+      </c>
+      <c r="D171" t="s">
+        <v>29</v>
+      </c>
+      <c r="F171" t="s">
+        <v>23</v>
+      </c>
+      <c r="G171" t="s">
         <v>100</v>
       </c>
-      <c r="H171" s="1" t="s">
+      <c r="H171" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A172" s="1" t="s">
+      <c r="A172" t="s">
         <v>87</v>
       </c>
-      <c r="B172" s="1">
+      <c r="B172">
         <v>0.84199999999999997</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G172" s="1" t="s">
+      <c r="C172" t="s">
+        <v>26</v>
+      </c>
+      <c r="D172" t="s">
+        <v>29</v>
+      </c>
+      <c r="F172" t="s">
+        <v>23</v>
+      </c>
+      <c r="G172" t="s">
         <v>88</v>
       </c>
-      <c r="H172" s="1" t="s">
+      <c r="H172" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A174" s="5" t="s">
+      <c r="A174" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="B174" s="4" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A175" s="1" t="s">
+      <c r="A175" t="s">
         <v>4</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B175" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A176" s="1" t="s">
+      <c r="A176" t="s">
         <v>5</v>
       </c>
-      <c r="B176" s="1">
+      <c r="B176">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A177" s="1" t="s">
+      <c r="A177" t="s">
         <v>6</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B177" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A178" s="1" t="s">
+      <c r="A178" t="s">
         <v>8</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B178" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A179" s="1" t="s">
+      <c r="A179" t="s">
         <v>10</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B179" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A180" s="1" t="s">
+      <c r="A180" t="s">
         <v>12</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B180" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A181" s="1" t="s">
+      <c r="A181" t="s">
         <v>13</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B181" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A182" s="1" t="s">
+      <c r="A182" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A183" s="5" t="s">
+      <c r="A183" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="C183" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="5" t="s">
+      <c r="D183" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E183" s="5" t="s">
+      <c r="E183" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F183" s="5" t="s">
+      <c r="F183" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G183" s="5" t="s">
+      <c r="G183" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H183" s="5" t="s">
+      <c r="H183" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A184" s="1" t="s">
+      <c r="A184" t="s">
         <v>113</v>
       </c>
-      <c r="B184" s="1">
+      <c r="B184">
         <v>1</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F184" s="1" t="s">
+      <c r="C184" t="s">
+        <v>26</v>
+      </c>
+      <c r="D184" t="s">
+        <v>29</v>
+      </c>
+      <c r="F184" t="s">
         <v>18</v>
       </c>
-      <c r="G184" s="1" t="s">
+      <c r="G184" t="s">
         <v>114</v>
       </c>
-      <c r="H184" s="1" t="s">
+      <c r="H184" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A185" s="1" t="s">
+      <c r="A185" t="s">
         <v>99</v>
       </c>
-      <c r="B185" s="1">
+      <c r="B185">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G185" s="1" t="s">
+      <c r="C185" t="s">
+        <v>26</v>
+      </c>
+      <c r="D185" t="s">
+        <v>29</v>
+      </c>
+      <c r="F185" t="s">
+        <v>23</v>
+      </c>
+      <c r="G185" t="s">
         <v>100</v>
       </c>
-      <c r="H185" s="1" t="s">
+      <c r="H185" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A186" s="1" t="s">
+      <c r="A186" t="s">
         <v>87</v>
       </c>
-      <c r="B186" s="1">
+      <c r="B186">
         <v>0.183</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G186" s="1" t="s">
+      <c r="C186" t="s">
+        <v>26</v>
+      </c>
+      <c r="D186" t="s">
+        <v>29</v>
+      </c>
+      <c r="F186" t="s">
+        <v>23</v>
+      </c>
+      <c r="G186" t="s">
         <v>88</v>
       </c>
-      <c r="H186" s="1" t="s">
+      <c r="H186" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A187" s="1" t="s">
+      <c r="A187" t="s">
         <v>79</v>
       </c>
-      <c r="B187" s="1">
+      <c r="B187">
         <v>0.78100000000000003</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G187" s="1" t="s">
+      <c r="C187" t="s">
+        <v>26</v>
+      </c>
+      <c r="D187" t="s">
+        <v>29</v>
+      </c>
+      <c r="F187" t="s">
+        <v>23</v>
+      </c>
+      <c r="G187" t="s">
         <v>80</v>
       </c>
-      <c r="H187" s="1" t="s">
+      <c r="H187" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A189" s="5" t="s">
+      <c r="A189" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B189" s="4" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A190" s="1" t="s">
+      <c r="A190" t="s">
         <v>4</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B190" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A191" s="1" t="s">
+      <c r="A191" t="s">
         <v>5</v>
       </c>
-      <c r="B191" s="1">
+      <c r="B191">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A192" s="1" t="s">
+      <c r="A192" t="s">
         <v>6</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B192" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A193" s="1" t="s">
+      <c r="A193" t="s">
         <v>8</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="B193" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A194" s="1" t="s">
+      <c r="A194" t="s">
         <v>10</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="B194" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A195" s="1" t="s">
+      <c r="A195" t="s">
         <v>12</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="B195" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A196" s="1" t="s">
+      <c r="A196" t="s">
         <v>13</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B196" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A197" s="1" t="s">
+      <c r="A197" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A198" s="5" t="s">
+      <c r="A198" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B198" s="5" t="s">
+      <c r="B198" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C198" s="5" t="s">
+      <c r="C198" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="5" t="s">
+      <c r="D198" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E198" s="5" t="s">
+      <c r="E198" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F198" s="5" t="s">
+      <c r="F198" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G198" s="5" t="s">
+      <c r="G198" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H198" s="5" t="s">
+      <c r="H198" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A199" s="1" t="s">
+      <c r="A199" t="s">
         <v>115</v>
       </c>
-      <c r="B199" s="1">
+      <c r="B199">
         <v>1</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D199" s="1" t="s">
+      <c r="C199" t="s">
+        <v>26</v>
+      </c>
+      <c r="D199" t="s">
         <v>116</v>
       </c>
-      <c r="F199" s="1" t="s">
+      <c r="F199" t="s">
         <v>18</v>
       </c>
-      <c r="G199" s="1" t="s">
+      <c r="G199" t="s">
         <v>114</v>
       </c>
-      <c r="H199" s="1" t="s">
+      <c r="H199" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A200" s="1" t="s">
+      <c r="A200" t="s">
         <v>111</v>
       </c>
-      <c r="B200" s="1">
+      <c r="B200">
         <v>0.80800000000000005</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G200" s="1" t="s">
+      <c r="C200" t="s">
+        <v>26</v>
+      </c>
+      <c r="D200" t="s">
+        <v>29</v>
+      </c>
+      <c r="F200" t="s">
+        <v>23</v>
+      </c>
+      <c r="G200" t="s">
         <v>112</v>
       </c>
-      <c r="H200" s="1" t="s">
+      <c r="H200" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A201" s="1" t="s">
+      <c r="A201" t="s">
         <v>113</v>
       </c>
-      <c r="B201" s="1">
+      <c r="B201">
         <v>1.23</v>
       </c>
-      <c r="C201" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G201" s="1" t="s">
+      <c r="C201" t="s">
+        <v>26</v>
+      </c>
+      <c r="D201" t="s">
+        <v>29</v>
+      </c>
+      <c r="F201" t="s">
+        <v>23</v>
+      </c>
+      <c r="G201" t="s">
         <v>114</v>
       </c>
-      <c r="H201" s="1" t="s">
+      <c r="H201" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A202" s="1" t="s">
+      <c r="A202" t="s">
         <v>117</v>
       </c>
-      <c r="B202" s="1">
+      <c r="B202">
         <v>12.8</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D202" s="1" t="s">
+      <c r="C202" t="s">
+        <v>26</v>
+      </c>
+      <c r="D202" t="s">
         <v>118</v>
       </c>
-      <c r="F202" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G202" s="1" t="s">
+      <c r="F202" t="s">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
         <v>119</v>
       </c>
-      <c r="H202" s="1" t="s">
+      <c r="H202" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A204" s="5" t="s">
+      <c r="A204" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B204" s="5" t="s">
+      <c r="B204" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A205" s="1" t="s">
+      <c r="A205" t="s">
         <v>4</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="B205" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A206" s="1" t="s">
+      <c r="A206" t="s">
         <v>5</v>
       </c>
-      <c r="B206" s="1">
+      <c r="B206">
         <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A207" s="1" t="s">
+      <c r="A207" t="s">
         <v>6</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="B207" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A208" s="1" t="s">
+      <c r="A208" t="s">
         <v>8</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="B208" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A209" s="1" t="s">
+      <c r="A209" t="s">
         <v>10</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="B209" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A210" s="1" t="s">
+      <c r="A210" t="s">
         <v>12</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="B210" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A211" s="1" t="s">
+      <c r="A211" t="s">
         <v>13</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="B211" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A212" s="1" t="s">
+      <c r="A212" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A213" s="5" t="s">
+      <c r="A213" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B213" s="5" t="s">
+      <c r="B213" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C213" s="5" t="s">
+      <c r="C213" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="5" t="s">
+      <c r="D213" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E213" s="5" t="s">
+      <c r="E213" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F213" s="5" t="s">
+      <c r="F213" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G213" s="5" t="s">
+      <c r="G213" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H213" s="5" t="s">
+      <c r="H213" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A214" s="1" t="s">
+      <c r="A214" t="s">
         <v>120</v>
       </c>
-      <c r="B214" s="1">
+      <c r="B214">
         <v>1</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D214" s="1" t="s">
+      <c r="C214" t="s">
+        <v>26</v>
+      </c>
+      <c r="D214" t="s">
         <v>116</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="F214" t="s">
         <v>18</v>
       </c>
-      <c r="G214" s="1" t="s">
+      <c r="G214" t="s">
         <v>120</v>
       </c>
-      <c r="H214" s="1" t="s">
+      <c r="H214" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A215" s="1" t="s">
+      <c r="A215" t="s">
         <v>121</v>
       </c>
-      <c r="B215" s="1">
+      <c r="B215">
         <v>10</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="C215" t="s">
         <v>21</v>
       </c>
-      <c r="D215" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G215" s="1" t="s">
+      <c r="D215" t="s">
+        <v>29</v>
+      </c>
+      <c r="F215" t="s">
+        <v>23</v>
+      </c>
+      <c r="G215" t="s">
         <v>122</v>
       </c>
-      <c r="H215" s="1" t="s">
+      <c r="H215" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A216" s="1" t="s">
+      <c r="A216" t="s">
         <v>238</v>
       </c>
-      <c r="B216" s="1">
+      <c r="B216">
         <v>5.8</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D216" s="1" t="s">
+      <c r="C216" t="s">
+        <v>26</v>
+      </c>
+      <c r="D216" t="s">
         <v>118</v>
       </c>
-      <c r="F216" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G216" s="1" t="s">
+      <c r="F216" t="s">
+        <v>23</v>
+      </c>
+      <c r="G216" t="s">
         <v>239</v>
       </c>
-      <c r="H216" s="1" t="s">
+      <c r="H216" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A217" s="1" t="s">
+      <c r="A217" t="s">
         <v>123</v>
       </c>
-      <c r="B217" s="1">
+      <c r="B217">
         <v>1.3499999999999999E-5</v>
       </c>
-      <c r="D217" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E217" s="1" t="s">
+      <c r="D217" t="s">
+        <v>29</v>
+      </c>
+      <c r="E217" t="s">
         <v>124</v>
       </c>
-      <c r="F217" s="1" t="s">
+      <c r="F217" t="s">
         <v>125</v>
       </c>
-      <c r="H217" s="1" t="s">
+      <c r="H217" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A219" s="5" t="s">
+      <c r="A219" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B219" s="5" t="s">
+      <c r="B219" s="4" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A220" s="1" t="s">
+      <c r="A220" t="s">
         <v>4</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="B220" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A221" s="1" t="s">
+      <c r="A221" t="s">
         <v>5</v>
       </c>
-      <c r="B221" s="1">
+      <c r="B221">
         <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A222" s="1" t="s">
+      <c r="A222" t="s">
         <v>6</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="B222" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A223" s="1" t="s">
+      <c r="A223" t="s">
         <v>8</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="B223" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A224" s="1" t="s">
+      <c r="A224" t="s">
         <v>10</v>
       </c>
-      <c r="B224" s="1" t="s">
+      <c r="B224" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A225" s="1" t="s">
+      <c r="A225" t="s">
         <v>12</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="B225" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A226" s="1" t="s">
+      <c r="A226" t="s">
         <v>13</v>
       </c>
-      <c r="B226" s="1" t="s">
+      <c r="B226" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A227" s="1" t="s">
+      <c r="A227" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A228" s="5" t="s">
+      <c r="A228" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C228" s="5" t="s">
+      <c r="C228" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="5" t="s">
+      <c r="D228" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E228" s="5" t="s">
+      <c r="E228" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F228" s="5" t="s">
+      <c r="F228" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="G228" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H228" s="5" t="s">
+      <c r="H228" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A229" s="1" t="s">
+      <c r="A229" t="s">
         <v>126</v>
       </c>
-      <c r="B229" s="1">
+      <c r="B229">
         <v>1</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D229" s="1" t="s">
+      <c r="C229" t="s">
+        <v>26</v>
+      </c>
+      <c r="D229" t="s">
         <v>116</v>
       </c>
-      <c r="F229" s="1" t="s">
+      <c r="F229" t="s">
         <v>18</v>
       </c>
-      <c r="G229" s="1" t="s">
+      <c r="G229" t="s">
         <v>126</v>
       </c>
-      <c r="H229" s="1" t="s">
+      <c r="H229" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A230" s="1" t="s">
+      <c r="A230" t="s">
         <v>127</v>
       </c>
-      <c r="B230" s="1">
+      <c r="B230">
         <v>50</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D230" s="1" t="s">
+      <c r="C230" t="s">
+        <v>26</v>
+      </c>
+      <c r="D230" t="s">
         <v>128</v>
       </c>
-      <c r="F230" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G230" s="1" t="s">
+      <c r="F230" t="s">
+        <v>23</v>
+      </c>
+      <c r="G230" t="s">
         <v>127</v>
       </c>
-      <c r="H230" s="1" t="s">
+      <c r="H230" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A232" s="5" t="s">
+      <c r="A232" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B232" s="5" t="s">
+      <c r="B232" s="4" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A233" s="1" t="s">
+      <c r="A233" t="s">
         <v>4</v>
       </c>
-      <c r="B233" s="1" t="s">
+      <c r="B233" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A234" s="1" t="s">
+      <c r="A234" t="s">
         <v>5</v>
       </c>
-      <c r="B234" s="1">
+      <c r="B234">
         <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A235" s="1" t="s">
+      <c r="A235" t="s">
         <v>6</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B235" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A236" s="1" t="s">
+      <c r="A236" t="s">
         <v>8</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="B236" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A237" s="1" t="s">
+      <c r="A237" t="s">
         <v>10</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="B237" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A238" s="1" t="s">
+      <c r="A238" t="s">
         <v>12</v>
       </c>
-      <c r="B238" s="1" t="s">
+      <c r="B238" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A239" s="1" t="s">
+      <c r="A239" t="s">
         <v>13</v>
       </c>
-      <c r="B239" s="1" t="s">
+      <c r="B239" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A240" s="1" t="s">
+      <c r="A240" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A241" s="5" t="s">
+      <c r="A241" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B241" s="5" t="s">
+      <c r="B241" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C241" s="5" t="s">
+      <c r="C241" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="5" t="s">
+      <c r="D241" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E241" s="5" t="s">
+      <c r="E241" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F241" s="5" t="s">
+      <c r="F241" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G241" s="5" t="s">
+      <c r="G241" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H241" s="5" t="s">
+      <c r="H241" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A242" s="1" t="s">
+      <c r="A242" t="s">
         <v>129</v>
       </c>
-      <c r="B242" s="1">
+      <c r="B242">
         <v>1</v>
       </c>
-      <c r="C242" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D242" s="1" t="s">
+      <c r="C242" t="s">
+        <v>26</v>
+      </c>
+      <c r="D242" t="s">
         <v>10</v>
       </c>
-      <c r="F242" s="1" t="s">
+      <c r="F242" t="s">
         <v>18</v>
       </c>
-      <c r="G242" s="1" t="s">
+      <c r="G242" t="s">
         <v>130</v>
       </c>
-      <c r="H242" s="1" t="s">
+      <c r="H242" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A243" s="1" t="s">
+      <c r="A243" t="s">
         <v>131</v>
       </c>
-      <c r="B243" s="1">
+      <c r="B243">
         <v>6</v>
       </c>
-      <c r="C243" s="1" t="s">
+      <c r="C243" t="s">
         <v>21</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="D243" t="s">
         <v>10</v>
       </c>
-      <c r="F243" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G243" s="1" t="s">
+      <c r="F243" t="s">
+        <v>23</v>
+      </c>
+      <c r="G243" t="s">
         <v>132</v>
       </c>
-      <c r="H243" s="1" t="s">
+      <c r="H243" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A244" s="1" t="s">
+      <c r="A244" t="s">
         <v>85</v>
       </c>
-      <c r="B244" s="1">
+      <c r="B244">
         <v>1</v>
       </c>
-      <c r="C244" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D244" s="1" t="s">
+      <c r="C244" t="s">
+        <v>26</v>
+      </c>
+      <c r="D244" t="s">
         <v>10</v>
       </c>
-      <c r="F244" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G244" s="1" t="s">
+      <c r="F244" t="s">
+        <v>23</v>
+      </c>
+      <c r="G244" t="s">
         <v>86</v>
       </c>
-      <c r="H244" s="1" t="s">
+      <c r="H244" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A245" s="1" t="s">
+      <c r="A245" t="s">
         <v>25</v>
       </c>
-      <c r="B245" s="1">
+      <c r="B245">
         <v>1</v>
       </c>
-      <c r="C245" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D245" s="1" t="s">
+      <c r="C245" t="s">
+        <v>26</v>
+      </c>
+      <c r="D245" t="s">
         <v>10</v>
       </c>
-      <c r="F245" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G245" s="1" t="s">
+      <c r="F245" t="s">
+        <v>23</v>
+      </c>
+      <c r="G245" t="s">
         <v>27</v>
       </c>
-      <c r="H245" s="1" t="s">
+      <c r="H245" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A247" s="5" t="s">
+      <c r="A247" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B247" s="5" t="s">
+      <c r="B247" s="4" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A248" s="1" t="s">
+      <c r="A248" t="s">
         <v>4</v>
       </c>
-      <c r="B248" s="1" t="s">
+      <c r="B248" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A249" s="1" t="s">
+      <c r="A249" t="s">
         <v>5</v>
       </c>
-      <c r="B249" s="1">
+      <c r="B249">
         <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A250" s="1" t="s">
+      <c r="A250" t="s">
         <v>6</v>
       </c>
-      <c r="B250" s="1" t="s">
+      <c r="B250" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A251" s="1" t="s">
+      <c r="A251" t="s">
         <v>8</v>
       </c>
-      <c r="B251" s="1" t="s">
+      <c r="B251" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A252" s="1" t="s">
+      <c r="A252" t="s">
         <v>10</v>
       </c>
-      <c r="B252" s="1" t="s">
+      <c r="B252" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A253" s="1" t="s">
+      <c r="A253" t="s">
         <v>12</v>
       </c>
-      <c r="B253" s="1" t="s">
+      <c r="B253" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A254" s="1" t="s">
+      <c r="A254" t="s">
         <v>13</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="B254" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A255" s="1" t="s">
+      <c r="A255" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A256" s="5" t="s">
+      <c r="A256" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B256" s="5" t="s">
+      <c r="B256" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C256" s="5" t="s">
+      <c r="C256" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="5" t="s">
+      <c r="D256" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E256" s="5" t="s">
+      <c r="E256" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F256" s="5" t="s">
+      <c r="F256" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G256" s="5" t="s">
+      <c r="G256" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H256" s="5" t="s">
+      <c r="H256" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A257" s="1" t="s">
+      <c r="A257" t="s">
         <v>133</v>
       </c>
-      <c r="B257" s="1">
+      <c r="B257">
         <v>1</v>
       </c>
-      <c r="C257" s="1" t="s">
+      <c r="C257" t="s">
         <v>152</v>
       </c>
-      <c r="D257" s="1" t="s">
+      <c r="D257" t="s">
         <v>10</v>
       </c>
-      <c r="F257" s="1" t="s">
+      <c r="F257" t="s">
         <v>18</v>
       </c>
-      <c r="G257" s="1" t="s">
+      <c r="G257" t="s">
         <v>134</v>
       </c>
-      <c r="H257" s="1" t="s">
+      <c r="H257" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A258" s="1" t="s">
+      <c r="A258" t="s">
         <v>28</v>
       </c>
-      <c r="B258" s="1">
+      <c r="B258">
         <v>221982</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="C258" t="s">
         <v>21</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F258" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G258" s="1" t="s">
+      <c r="D258" t="s">
+        <v>29</v>
+      </c>
+      <c r="F258" t="s">
+        <v>23</v>
+      </c>
+      <c r="G258" t="s">
         <v>30</v>
       </c>
-      <c r="H258" s="1" t="s">
+      <c r="H258" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A259" s="1" t="s">
+      <c r="A259" t="s">
         <v>34</v>
       </c>
-      <c r="B259" s="1">
+      <c r="B259">
         <v>345901</v>
       </c>
-      <c r="C259" s="1" t="s">
+      <c r="C259" t="s">
         <v>21</v>
       </c>
-      <c r="D259" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F259" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G259" s="1" t="s">
+      <c r="D259" t="s">
+        <v>29</v>
+      </c>
+      <c r="F259" t="s">
+        <v>23</v>
+      </c>
+      <c r="G259" t="s">
         <v>35</v>
       </c>
-      <c r="H259" s="1" t="s">
+      <c r="H259" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A260" s="1" t="s">
+      <c r="A260" t="s">
         <v>135</v>
       </c>
-      <c r="B260" s="1">
+      <c r="B260">
         <v>475722</v>
       </c>
-      <c r="C260" s="1" t="s">
+      <c r="C260" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D260" t="s">
+        <v>29</v>
+      </c>
+      <c r="F260" t="s">
+        <v>23</v>
+      </c>
+      <c r="G260" t="s">
+        <v>136</v>
+      </c>
+      <c r="H260" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>137</v>
+      </c>
+      <c r="B261">
+        <v>550</v>
+      </c>
+      <c r="C261" t="s">
         <v>21</v>
       </c>
-      <c r="D260" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F260" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G260" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H260" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A261" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B261" s="1">
-        <v>550</v>
-      </c>
-      <c r="C261" s="1" t="s">
+      <c r="D261" t="s">
+        <v>29</v>
+      </c>
+      <c r="F261" t="s">
+        <v>23</v>
+      </c>
+      <c r="G261" t="s">
+        <v>138</v>
+      </c>
+      <c r="H261" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>53</v>
+      </c>
+      <c r="B262">
+        <v>416</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D262" t="s">
+        <v>29</v>
+      </c>
+      <c r="F262" t="s">
+        <v>23</v>
+      </c>
+      <c r="G262" t="s">
+        <v>54</v>
+      </c>
+      <c r="H262" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>139</v>
+      </c>
+      <c r="B263">
+        <v>343</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D263" t="s">
+        <v>29</v>
+      </c>
+      <c r="F263" t="s">
+        <v>23</v>
+      </c>
+      <c r="G263" t="s">
+        <v>140</v>
+      </c>
+      <c r="H263" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>141</v>
+      </c>
+      <c r="B264">
+        <v>90</v>
+      </c>
+      <c r="C264" t="s">
         <v>21</v>
       </c>
-      <c r="D261" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F261" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H261" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A262" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B262" s="1">
-        <v>416</v>
-      </c>
-      <c r="C262" s="1" t="s">
+      <c r="D264" t="s">
+        <v>29</v>
+      </c>
+      <c r="F264" t="s">
+        <v>23</v>
+      </c>
+      <c r="G264" t="s">
+        <v>142</v>
+      </c>
+      <c r="H264" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>59</v>
+      </c>
+      <c r="B265">
+        <v>55</v>
+      </c>
+      <c r="C265" t="s">
         <v>21</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F262" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H262" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A263" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B263" s="1">
-        <v>343</v>
-      </c>
-      <c r="C263" s="1" t="s">
+      <c r="D265" t="s">
+        <v>29</v>
+      </c>
+      <c r="F265" t="s">
+        <v>23</v>
+      </c>
+      <c r="G265" t="s">
+        <v>60</v>
+      </c>
+      <c r="H265" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>143</v>
+      </c>
+      <c r="B266">
+        <v>6383</v>
+      </c>
+      <c r="C266" t="s">
         <v>21</v>
       </c>
-      <c r="D263" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F263" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G263" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H263" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A264" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B264" s="1">
-        <v>90</v>
-      </c>
-      <c r="C264" s="1" t="s">
+      <c r="D266" t="s">
+        <v>29</v>
+      </c>
+      <c r="F266" t="s">
+        <v>23</v>
+      </c>
+      <c r="G266" t="s">
+        <v>144</v>
+      </c>
+      <c r="H266" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>145</v>
+      </c>
+      <c r="B267">
+        <v>460</v>
+      </c>
+      <c r="C267" t="s">
         <v>21</v>
       </c>
-      <c r="D264" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F264" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G264" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H264" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A265" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B265" s="1">
+      <c r="D267" t="s">
+        <v>29</v>
+      </c>
+      <c r="F267" t="s">
+        <v>23</v>
+      </c>
+      <c r="G267" t="s">
+        <v>146</v>
+      </c>
+      <c r="H267" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>147</v>
+      </c>
+      <c r="B268">
         <v>55</v>
       </c>
-      <c r="C265" s="1" t="s">
+      <c r="C268" t="s">
         <v>21</v>
       </c>
-      <c r="D265" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F265" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G265" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H265" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A266" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B266" s="1">
-        <v>6383</v>
-      </c>
-      <c r="C266" s="1" t="s">
+      <c r="D268" t="s">
+        <v>29</v>
+      </c>
+      <c r="F268" t="s">
+        <v>23</v>
+      </c>
+      <c r="G268" t="s">
+        <v>148</v>
+      </c>
+      <c r="H268" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>260</v>
+      </c>
+      <c r="B269">
+        <v>423.30339999999995</v>
+      </c>
+      <c r="C269" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D266" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F266" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H266" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A267" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B267" s="1">
-        <v>460</v>
-      </c>
-      <c r="C267" s="1" t="s">
+      <c r="D269" t="s">
+        <v>29</v>
+      </c>
+      <c r="F269" t="s">
+        <v>23</v>
+      </c>
+      <c r="G269" t="s">
+        <v>261</v>
+      </c>
+      <c r="H269" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>263</v>
+      </c>
+      <c r="B270">
+        <v>1995</v>
+      </c>
+      <c r="C270" t="s">
+        <v>26</v>
+      </c>
+      <c r="D270" t="s">
+        <v>128</v>
+      </c>
+      <c r="F270" t="s">
+        <v>23</v>
+      </c>
+      <c r="G270" t="s">
+        <v>263</v>
+      </c>
+      <c r="H270" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>126</v>
+      </c>
+      <c r="B271">
+        <v>41</v>
+      </c>
+      <c r="C271" t="s">
+        <v>26</v>
+      </c>
+      <c r="D271" t="s">
+        <v>116</v>
+      </c>
+      <c r="F271" t="s">
+        <v>23</v>
+      </c>
+      <c r="G271" t="s">
+        <v>126</v>
+      </c>
+      <c r="H271" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>120</v>
+      </c>
+      <c r="B272">
+        <v>2025</v>
+      </c>
+      <c r="C272" t="s">
+        <v>26</v>
+      </c>
+      <c r="D272" t="s">
+        <v>116</v>
+      </c>
+      <c r="F272" t="s">
+        <v>23</v>
+      </c>
+      <c r="G272" t="s">
+        <v>120</v>
+      </c>
+      <c r="H272" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>115</v>
+      </c>
+      <c r="B273">
+        <v>2025</v>
+      </c>
+      <c r="C273" t="s">
+        <v>26</v>
+      </c>
+      <c r="D273" t="s">
+        <v>116</v>
+      </c>
+      <c r="F273" t="s">
+        <v>23</v>
+      </c>
+      <c r="G273" t="s">
+        <v>114</v>
+      </c>
+      <c r="H273" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>129</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274" t="s">
+        <v>26</v>
+      </c>
+      <c r="D274" t="s">
+        <v>10</v>
+      </c>
+      <c r="F274" t="s">
+        <v>23</v>
+      </c>
+      <c r="G274" t="s">
+        <v>130</v>
+      </c>
+      <c r="H274" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>3</v>
+      </c>
+      <c r="B275">
+        <v>120</v>
+      </c>
+      <c r="C275" t="s">
+        <v>152</v>
+      </c>
+      <c r="D275" t="s">
+        <v>11</v>
+      </c>
+      <c r="F275" t="s">
+        <v>23</v>
+      </c>
+      <c r="G275" t="s">
+        <v>7</v>
+      </c>
+      <c r="H275" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>19</v>
+      </c>
+      <c r="B276">
+        <v>14.1</v>
+      </c>
+      <c r="C276" t="s">
+        <v>152</v>
+      </c>
+      <c r="D276" t="s">
+        <v>11</v>
+      </c>
+      <c r="F276" t="s">
+        <v>23</v>
+      </c>
+      <c r="G276" t="s">
+        <v>19</v>
+      </c>
+      <c r="H276" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>271</v>
+      </c>
+      <c r="B277">
+        <v>988.2</v>
+      </c>
+      <c r="C277" t="s">
+        <v>26</v>
+      </c>
+      <c r="D277" t="s">
+        <v>272</v>
+      </c>
+      <c r="F277" t="s">
+        <v>23</v>
+      </c>
+      <c r="G277" t="s">
+        <v>273</v>
+      </c>
+      <c r="H277" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>275</v>
+      </c>
+      <c r="B278">
+        <v>73443.08</v>
+      </c>
+      <c r="C278" t="s">
+        <v>26</v>
+      </c>
+      <c r="D278" t="s">
+        <v>272</v>
+      </c>
+      <c r="F278" t="s">
+        <v>23</v>
+      </c>
+      <c r="G278" t="s">
+        <v>276</v>
+      </c>
+      <c r="H278" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>5625</v>
+      </c>
+      <c r="C279" t="s">
         <v>21</v>
       </c>
-      <c r="D267" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F267" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G267" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H267" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A268" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B268" s="1">
-        <v>55</v>
-      </c>
-      <c r="C268" s="1" t="s">
+      <c r="D279" t="s">
+        <v>272</v>
+      </c>
+      <c r="F279" t="s">
+        <v>23</v>
+      </c>
+      <c r="G279" t="s">
+        <v>279</v>
+      </c>
+      <c r="H279" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>257171610</v>
+      </c>
+      <c r="C280" t="s">
         <v>21</v>
       </c>
-      <c r="D268" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F268" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G268" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H268" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A269" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B269" s="1">
-        <v>423.30339999999995</v>
-      </c>
-      <c r="C269" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F269" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G269" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="H269" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A270" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B270" s="1">
-        <v>1995</v>
-      </c>
-      <c r="C270" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D270" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F270" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G270" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="H270" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A271" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B271" s="1">
-        <v>41</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F271" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G271" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H271" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A272" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B272" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F272" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G272" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H272" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A273" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B273" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F273" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H273" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A274" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B274" s="1">
+      <c r="D280" t="s">
+        <v>272</v>
+      </c>
+      <c r="F280" t="s">
+        <v>23</v>
+      </c>
+      <c r="G280" t="s">
+        <v>279</v>
+      </c>
+      <c r="H280" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>282</v>
+      </c>
+      <c r="B281">
+        <v>-56843.3</v>
+      </c>
+      <c r="C281" t="s">
+        <v>283</v>
+      </c>
+      <c r="D281" t="s">
+        <v>29</v>
+      </c>
+      <c r="F281" t="s">
+        <v>23</v>
+      </c>
+      <c r="G281" t="s">
+        <v>284</v>
+      </c>
+      <c r="H281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>286</v>
+      </c>
+      <c r="B282">
+        <v>-475722</v>
+      </c>
+      <c r="C282" t="s">
+        <v>32</v>
+      </c>
+      <c r="D282" t="s">
+        <v>29</v>
+      </c>
+      <c r="F282" t="s">
+        <v>23</v>
+      </c>
+      <c r="G282" t="s">
+        <v>287</v>
+      </c>
+      <c r="H282" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>289</v>
+      </c>
+      <c r="B283">
+        <v>-849</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D283" t="s">
+        <v>29</v>
+      </c>
+      <c r="F283" t="s">
+        <v>23</v>
+      </c>
+      <c r="G283" t="s">
+        <v>290</v>
+      </c>
+      <c r="H283" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>292</v>
+      </c>
+      <c r="B284">
+        <v>-55</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D284" t="s">
+        <v>29</v>
+      </c>
+      <c r="F284" t="s">
+        <v>23</v>
+      </c>
+      <c r="G284" t="s">
+        <v>293</v>
+      </c>
+      <c r="H284" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A287" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B287" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>4</v>
+      </c>
+      <c r="B288" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>5</v>
+      </c>
+      <c r="B289">
         <v>1</v>
       </c>
-      <c r="C274" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D274" s="1" t="s">
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>6</v>
+      </c>
+      <c r="B290" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>8</v>
+      </c>
+      <c r="B291" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
         <v>10</v>
       </c>
-      <c r="F274" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G274" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H274" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A275" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B275" s="1">
-        <v>120</v>
-      </c>
-      <c r="C275" s="1" t="s">
+      <c r="B292" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>12</v>
+      </c>
+      <c r="B293" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>13</v>
+      </c>
+      <c r="B294" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A296" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>149</v>
+      </c>
+      <c r="B298">
+        <v>1</v>
+      </c>
+      <c r="C298" t="s">
         <v>152</v>
       </c>
-      <c r="D275" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F275" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H275" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A276" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B276" s="1">
-        <v>14.1</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F276" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G276" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H276" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A277" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B277" s="1">
-        <v>988.2</v>
-      </c>
-      <c r="C277" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F277" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H277" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A278" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B278" s="1">
-        <v>73443.08</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F278" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="H278" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A279" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B279" s="1">
-        <v>5625</v>
-      </c>
-      <c r="C279" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F279" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="H279" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A280" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B280" s="1">
-        <v>257171610</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="H280" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A281" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B281" s="1">
-        <v>-56843.3</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F281" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="H281" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A282" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B282" s="1">
-        <v>-475722</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="H282" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A283" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B283" s="1">
-        <v>-849</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F283" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="H283" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A284" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B284" s="1">
-        <v>-55</v>
-      </c>
-      <c r="C284" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F284" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="H284" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A287" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B287" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A288" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A289" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B289" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A290" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B290" s="1" t="s">
+      <c r="D298" t="s">
+        <v>151</v>
+      </c>
+      <c r="F298" t="s">
+        <v>18</v>
+      </c>
+      <c r="G298" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A291" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B291" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A292" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B292" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A293" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B293" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A294" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A295" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A296" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B296" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C296" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D296" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E296" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G296" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H296" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A298" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B298" s="1">
-        <v>1</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F298" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H298" s="1" t="s">
+      <c r="H298" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A299" s="1" t="s">
+      <c r="A299" t="s">
         <v>133</v>
       </c>
-      <c r="B299" s="1">
+      <c r="B299">
         <f>1/(2.97*1000000*20)</f>
         <v>1.6835016835016835E-8</v>
       </c>
-      <c r="C299" s="1" t="s">
+      <c r="C299" t="s">
         <v>152</v>
       </c>
-      <c r="D299" s="1" t="s">
+      <c r="D299" t="s">
         <v>10</v>
       </c>
-      <c r="F299" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G299" s="1" t="s">
+      <c r="F299" t="s">
+        <v>23</v>
+      </c>
+      <c r="G299" t="s">
         <v>134</v>
       </c>
-      <c r="H299" s="1" t="s">
+      <c r="H299" t="s">
         <v>296</v>
       </c>
     </row>
